--- a/Extra/TestCase001.xlsx
+++ b/Extra/TestCase001.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000"/>
+    <workbookView windowWidth="23040" windowHeight="8400"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="105">
   <si>
     <t>TestCase</t>
   </si>
@@ -144,6 +144,204 @@
   </si>
   <si>
     <t>Người dùng có thể thay đổi được Avatar và nhì thấy Avatar của nhau</t>
+  </si>
+  <si>
+    <t>Sent_empty_message</t>
+  </si>
+  <si>
+    <t>Gửi tin nhắn không có nội dung (chỉ ấn Space hoặc Enter)</t>
+  </si>
+  <si>
+    <t>Nút gửi bị vô hiệu hóa hoặc hệ thống báo lỗi, không gửi tin nhắn rỗng lên Server.</t>
+  </si>
+  <si>
+    <t>Sent_max_length_text</t>
+  </si>
+  <si>
+    <t>Gửi một đoạn tin nhắn text có độ dài vượt quá giới hạn cho phép (ví dụ &gt; 4000 ký tự)</t>
+  </si>
+  <si>
+    <t>Hệ thống ngăn không cho nhập tiếp hoặc tự động cắt ngắn/báo lỗi quá ký tự.</t>
+  </si>
+  <si>
+    <t>Sent_huge_image</t>
+  </si>
+  <si>
+    <t>Gửi một hình ảnh có dung lượng cực lớn (ví dụ: file 50MB hoặc ảnh 8K)</t>
+  </si>
+  <si>
+    <t>Hệ thống giới hạn dung lượng, hiển thị cảnh báo file quá kích thước cho phép.</t>
+  </si>
+  <si>
+    <t>Sent_invalid_image_format</t>
+  </si>
+  <si>
+    <t>Đổi đuôi một file .txt hoặc .exe thành .png rồi gửi làm ảnh đại diện hoặc tin nhắn ảnh</t>
+  </si>
+  <si>
+    <t>Server kiểm tra mã file, từ chối file lỗi và hiển thị thông báo "Định dạng không hợp lệ".</t>
+  </si>
+  <si>
+    <t>Client_disconnect_suddenly</t>
+  </si>
+  <si>
+    <t>Client đang kết nối thì bị mất mạng đột ngột (Tắt Wi-Fi/Rút dây mạng)</t>
+  </si>
+  <si>
+    <t>Server nhận biết client mất kết nối (sau khoảng timeout), chuyển trạng thái client thành offline. Client hiển thị "Đang kết nối lại...".</t>
+  </si>
+  <si>
+    <t>Client_reconnect</t>
+  </si>
+  <si>
+    <t>Client có mạng trở lại sau khi bị mất kết nối</t>
+  </si>
+  <si>
+    <t>Client tự động kết nối lại thành công với Server mà không cần khởi động lại app; nhận được các tin nhắn bị lỡ.</t>
+  </si>
+  <si>
+    <t>Server_shutdown_unexpectedly</t>
+  </si>
+  <si>
+    <t>Server đột ngột bị sập khi các Client đang chat</t>
+  </si>
+  <si>
+    <t>Tất cả Client nhận được thông báo mất kết nối với Server, các chức năng gửi tin nhắn bị khóa tạm thời.</t>
+  </si>
+  <si>
+    <t>Forward_to_multiple_clients</t>
+  </si>
+  <si>
+    <t>Chuyển tiếp (Forward) một tin nhắn/hình ảnh cho nhiều người cùng lúc</t>
+  </si>
+  <si>
+    <t>Tin nhắn được gửi đồng thời đến tất cả các Client được chọn một cách chính xác.</t>
+  </si>
+  <si>
+    <t>Reply_deleted_message</t>
+  </si>
+  <si>
+    <t>Trả lời (Reply) một tin nhắn nhưng ngay sau đó tin nhắn gốc bị người kia xóa đi</t>
+  </si>
+  <si>
+    <t>Hệ thống xử lý mượt mà, hiển thị tin nhắn gốc dưới dạng "Tin nhắn đã bị xóa" trong phần Reply.</t>
+  </si>
+  <si>
+    <t>Concurrent_messages</t>
+  </si>
+  <si>
+    <t>Nhiều Client cùng gửi tin nhắn vào Group Chat tại cùng một thời điểm</t>
+  </si>
+  <si>
+    <t>Server xử lý đồng bộ (Concurrency Management), tin nhắn của các client xếp hàng và hiển thị đúng thứ tự thời gian trên tất cả các client.</t>
+  </si>
+  <si>
+    <t>Duplicate_login</t>
+  </si>
+  <si>
+    <t>Sử dụng cùng một tài khoản để đăng nhập trên 2 Client khác nhau</t>
+  </si>
+  <si>
+    <t>Client đầu tiên bị đăng xuất tự động kèm thông báo "Tài khoản được đăng nhập từ thiết bị khác".</t>
+  </si>
+  <si>
+    <t>SQL_Injection_chat</t>
+  </si>
+  <si>
+    <t>Nhập các chuỗi mã độc vào ô chat (ví dụ: ' OR '1'='1 hoặc &lt;script&gt;alert(1)&lt;/script&gt;)</t>
+  </si>
+  <si>
+    <t>Server/Client mã hóa dữ liệu (Sanitize/Escape), hiển thị dưới dạng text thuần túy, không bị lỗi bảo mật hoặc thực thi script.</t>
+  </si>
+  <si>
+    <t>Login_success</t>
+  </si>
+  <si>
+    <t>Đăng nhập với Username và Password hoàn toàn chính xác.</t>
+  </si>
+  <si>
+    <t>Đăng nhập thành công, chuyển hướng vào màn hình chat chính, hiển thị đúng thông tin user.</t>
+  </si>
+  <si>
+    <t>Login_wrong_password</t>
+  </si>
+  <si>
+    <t>Đăng nhập đúng Username nhưng nhập sai Password</t>
+  </si>
+  <si>
+    <t>Hiển thị thông báo lỗi rõ ràng: "Mật khẩu không chính xác", không cho phép vào hệ thống.</t>
+  </si>
+  <si>
+    <t>Login_non_existent_user</t>
+  </si>
+  <si>
+    <t>Đăng nhập với một Username chưa từng được đăng ký trong hệ thống.</t>
+  </si>
+  <si>
+    <t>Hiển thị thông báo lỗi thích hợp (ví dụ: "Tài khoản không tồn tại").</t>
+  </si>
+  <si>
+    <t>Login_empty_fields</t>
+  </si>
+  <si>
+    <t>Để trống cả Username và Password rồi nhấn nút Login, hoặc chỉ điền một trong hai</t>
+  </si>
+  <si>
+    <t>Hệ thống báo lỗi ngay tại client (Validation) yêu cầu nhập đầy đủ, không gửi request rỗng lên Server.</t>
+  </si>
+  <si>
+    <t>Login_brute_force_protection</t>
+  </si>
+  <si>
+    <t>Nhập sai mật khẩu liên tiếp nhiều lần (ví dụ: 5 lần) trên cùng một tài khoản.</t>
+  </si>
+  <si>
+    <t>Hệ thống tạm thời khóa tài khoản hoặc bắt nhập CAPTCHA / hiển thị đếm ngược thời gian chờ (ví dụ: "Thử lại sau 30 giây").</t>
+  </si>
+  <si>
+    <t>Login_case_sensitivity</t>
+  </si>
+  <si>
+    <t>Nhập Password đúng ký tự nhưng sai định dạng Hoa/Thường (ví dụ: mật khẩu là Abc@123 nhưng nhập abc@123).</t>
+  </si>
+  <si>
+    <t>Hệ thống từ chối đăng nhập (vì mật khẩu bắt buộc phải phân biệt chữ hoa/chữ thường).</t>
+  </si>
+  <si>
+    <t>Login_sql_injection</t>
+  </si>
+  <si>
+    <t>Nhập chuỗi SQL Injection vào ô Username (ví dụ: ' OR '1'='1) và mật khẩu bất kỳ.</t>
+  </si>
+  <si>
+    <t>Hệ thống báo lỗi tài khoản không hợp lệ, tuyệt đối không được để lọt qua cửa đăng nhập.</t>
+  </si>
+  <si>
+    <t>Login_trim_whitespace</t>
+  </si>
+  <si>
+    <t>Nhập Username có khoảng trắng thừa ở đầu hoặc cuối (ví dụ: user123 thay vì user123).</t>
+  </si>
+  <si>
+    <t>Hệ thống tự động cắt bỏ khoảng trắng thừa (Trim) và vẫn cho phép đăng nhập thành công (nếu ký tự gốc đúng).</t>
+  </si>
+  <si>
+    <t>Login_session_timeout</t>
+  </si>
+  <si>
+    <t>Đăng nhập thành công, sau đó treo ứng dụng/để máy treo qua đêm (hết hạn Session/Token).</t>
+  </si>
+  <si>
+    <t>Khi người dùng tương tác lại (ví dụ: gửi tin nhắn), hệ thống tự động đẩy ra màn hình Login và yêu cầu đăng nhập lại.</t>
+  </si>
+  <si>
+    <t>Login_network_interrupted</t>
+  </si>
+  <si>
+    <t>Nhấn nút Login đúng lúc mạng bị ngắt kết nối đột ngột.</t>
+  </si>
+  <si>
+    <t>Hệ thống hiển thị trạng thái loading (hoặc timeout) và báo lỗi "Kết nối mạng không ổn định", không bị crash app.</t>
   </si>
 </sst>
 </file>
@@ -1299,14 +1497,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="8.30555555555556" customWidth="1"/>
-    <col min="2" max="2" width="20.3796296296296" customWidth="1"/>
-    <col min="3" max="3" width="52.75" customWidth="1"/>
-    <col min="4" max="4" width="24.1481481481481" customWidth="1"/>
-    <col min="5" max="5" width="58.0648148148148" customWidth="1"/>
+    <col min="2" max="2" width="30.3333333333333" customWidth="1"/>
+    <col min="3" max="3" width="96.1296296296296" customWidth="1"/>
+    <col min="4" max="4" width="78.1574074074074" customWidth="1"/>
+    <col min="5" max="5" width="114.009259259259" customWidth="1"/>
     <col min="6" max="6" width="31.9722222222222" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1346,7 +1544,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <f t="shared" ref="A3:A11" si="0">A2+1</f>
+        <f t="shared" ref="A3:A34" si="0">A2+1</f>
         <v>2</v>
       </c>
       <c r="B3" t="s">
@@ -1465,6 +1663,10 @@
       </c>
     </row>
     <row r="11" spans="1:6">
+      <c r="A11">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
       <c r="B11" t="s">
         <v>33</v>
       </c>
@@ -1476,6 +1678,10 @@
       </c>
     </row>
     <row r="12" spans="1:6">
+      <c r="A12">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
       <c r="B12" t="s">
         <v>36</v>
       </c>
@@ -1484,6 +1690,336 @@
       </c>
       <c r="E12" t="s">
         <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C13" t="s">
+        <v>40</v>
+      </c>
+      <c r="E13" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>42</v>
+      </c>
+      <c r="C14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E14" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>45</v>
+      </c>
+      <c r="C15" t="s">
+        <v>46</v>
+      </c>
+      <c r="E15" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" t="s">
+        <v>49</v>
+      </c>
+      <c r="E16" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>51</v>
+      </c>
+      <c r="C17" t="s">
+        <v>52</v>
+      </c>
+      <c r="E17" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C18" t="s">
+        <v>55</v>
+      </c>
+      <c r="E18" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>57</v>
+      </c>
+      <c r="C19" t="s">
+        <v>58</v>
+      </c>
+      <c r="E19" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>60</v>
+      </c>
+      <c r="C20" t="s">
+        <v>61</v>
+      </c>
+      <c r="E20" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>63</v>
+      </c>
+      <c r="C21" t="s">
+        <v>64</v>
+      </c>
+      <c r="E21" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>66</v>
+      </c>
+      <c r="C22" t="s">
+        <v>67</v>
+      </c>
+      <c r="E22" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>69</v>
+      </c>
+      <c r="C23" t="s">
+        <v>70</v>
+      </c>
+      <c r="E23" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>72</v>
+      </c>
+      <c r="C24" t="s">
+        <v>73</v>
+      </c>
+      <c r="E24" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>75</v>
+      </c>
+      <c r="C25" t="s">
+        <v>76</v>
+      </c>
+      <c r="E25" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>78</v>
+      </c>
+      <c r="C26" t="s">
+        <v>79</v>
+      </c>
+      <c r="E26" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>81</v>
+      </c>
+      <c r="C27" t="s">
+        <v>82</v>
+      </c>
+      <c r="E27" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>84</v>
+      </c>
+      <c r="C28" t="s">
+        <v>85</v>
+      </c>
+      <c r="E28" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>87</v>
+      </c>
+      <c r="C29" t="s">
+        <v>88</v>
+      </c>
+      <c r="E29" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>90</v>
+      </c>
+      <c r="C30" t="s">
+        <v>91</v>
+      </c>
+      <c r="E30" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>93</v>
+      </c>
+      <c r="C31" t="s">
+        <v>94</v>
+      </c>
+      <c r="E31" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>96</v>
+      </c>
+      <c r="C32" t="s">
+        <v>97</v>
+      </c>
+      <c r="E32" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>99</v>
+      </c>
+      <c r="C33" t="s">
+        <v>100</v>
+      </c>
+      <c r="E33" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>102</v>
+      </c>
+      <c r="C34" t="s">
+        <v>103</v>
+      </c>
+      <c r="E34" t="s">
+        <v>104</v>
       </c>
     </row>
   </sheetData>

--- a/Extra/TestCase001.xlsx
+++ b/Extra/TestCase001.xlsx
@@ -7,7 +7,40 @@
     <workbookView windowWidth="23040" windowHeight="8400"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="test_case" sheetId="1" r:id="rId1"/>
+    <sheet name="01" sheetId="2" r:id="rId2"/>
+    <sheet name="02" sheetId="3" r:id="rId3"/>
+    <sheet name="03" sheetId="4" r:id="rId4"/>
+    <sheet name="04" sheetId="5" r:id="rId5"/>
+    <sheet name="05" sheetId="6" r:id="rId6"/>
+    <sheet name="06" sheetId="7" r:id="rId7"/>
+    <sheet name="07" sheetId="8" r:id="rId8"/>
+    <sheet name="08" sheetId="9" r:id="rId9"/>
+    <sheet name="09" sheetId="10" r:id="rId10"/>
+    <sheet name="10" sheetId="11" r:id="rId11"/>
+    <sheet name="11" sheetId="12" r:id="rId12"/>
+    <sheet name="12" sheetId="13" r:id="rId13"/>
+    <sheet name="13" sheetId="14" r:id="rId14"/>
+    <sheet name="14" sheetId="15" r:id="rId15"/>
+    <sheet name="15" sheetId="16" r:id="rId16"/>
+    <sheet name="16" sheetId="17" r:id="rId17"/>
+    <sheet name="17" sheetId="18" r:id="rId18"/>
+    <sheet name="18" sheetId="19" r:id="rId19"/>
+    <sheet name="19" sheetId="20" r:id="rId20"/>
+    <sheet name="20" sheetId="21" r:id="rId21"/>
+    <sheet name="21" sheetId="22" r:id="rId22"/>
+    <sheet name="22" sheetId="23" r:id="rId23"/>
+    <sheet name="23" sheetId="24" r:id="rId24"/>
+    <sheet name="24" sheetId="25" r:id="rId25"/>
+    <sheet name="25" sheetId="26" r:id="rId26"/>
+    <sheet name="26" sheetId="27" r:id="rId27"/>
+    <sheet name="27" sheetId="28" r:id="rId28"/>
+    <sheet name="28" sheetId="29" r:id="rId29"/>
+    <sheet name="29" sheetId="30" r:id="rId30"/>
+    <sheet name="30" sheetId="31" r:id="rId31"/>
+    <sheet name="31" sheetId="32" r:id="rId32"/>
+    <sheet name="32" sheetId="33" r:id="rId33"/>
+    <sheet name="33" sheetId="34" r:id="rId34"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="140">
   <si>
     <t>TestCase</t>
   </si>
@@ -53,9 +86,15 @@
     <t xml:space="preserve">Chạy sever và hiển thị trạng thái đang chờ client </t>
   </si>
   <si>
+    <t>Đạt</t>
+  </si>
+  <si>
     <t>Server chạy và hiển thị đang chờ Client</t>
   </si>
   <si>
+    <t>01 : đã hiển thị được đang chờ kết nối và cho biết tên người kết nối</t>
+  </si>
+  <si>
     <t>Run_client</t>
   </si>
   <si>
@@ -65,6 +104,9 @@
     <t>Client chạy và hiển thị đã kết nối với Server</t>
   </si>
   <si>
+    <t xml:space="preserve">02 : đã chạy thành công </t>
+  </si>
+  <si>
     <t>Sent_message</t>
   </si>
   <si>
@@ -74,6 +116,9 @@
     <t>có 1 đoạn tin nhắn bằng text giữa các Client</t>
   </si>
   <si>
+    <t>03 : thực hiện thành công</t>
+  </si>
+  <si>
     <t>Sent_picture</t>
   </si>
   <si>
@@ -83,6 +128,9 @@
     <t>Gửi hình ảnh qua lại giữa các Client</t>
   </si>
   <si>
+    <t>04 : thực hiện thành công</t>
+  </si>
+  <si>
     <t>Sent_sticker</t>
   </si>
   <si>
@@ -92,6 +140,9 @@
     <t>Gửi được sticker cho nhau</t>
   </si>
   <si>
+    <t>05 : đã gửi được sticker</t>
+  </si>
+  <si>
     <t>Sent_special_characters</t>
   </si>
   <si>
@@ -101,6 +152,9 @@
     <t>Gửi được các kí tự đặc biệt</t>
   </si>
   <si>
+    <t>06 : đã gửi được kí tự đặc biệt</t>
+  </si>
+  <si>
     <t>Sent_special_text</t>
   </si>
   <si>
@@ -110,6 +164,9 @@
     <t>Server có thể xử lí được cá kí hiệu đặc biệt</t>
   </si>
   <si>
+    <t xml:space="preserve">07 :server đã nhận và xử lí được các kí tự đặc biệt </t>
+  </si>
+  <si>
     <t xml:space="preserve">Sent_emoji </t>
   </si>
   <si>
@@ -119,6 +176,9 @@
     <t>Client có thể gửi các kí tự emoji cho nhau</t>
   </si>
   <si>
+    <t>08 : đã gửi được emoji giữa các client</t>
+  </si>
+  <si>
     <t>Feature_rely</t>
   </si>
   <si>
@@ -128,15 +188,24 @@
     <t xml:space="preserve">Có thể rely người khác trong group chat </t>
   </si>
   <si>
+    <t>09 : đã rely được cho người khác</t>
+  </si>
+  <si>
     <t>Feature_forward</t>
   </si>
   <si>
     <t>chuyển tiếp tin nhắn cho người khác</t>
   </si>
   <si>
+    <t>Chưa đạt</t>
+  </si>
+  <si>
     <t>Chuyển tiếp tin nhắn cho người khác</t>
   </si>
   <si>
+    <t>10 : chưa có chức năng chuyển tiếp</t>
+  </si>
+  <si>
     <t>Feature_avatar</t>
   </si>
   <si>
@@ -146,6 +215,9 @@
     <t>Người dùng có thể thay đổi được Avatar và nhì thấy Avatar của nhau</t>
   </si>
   <si>
+    <t>11 : đã có thể thay đổi avatar nhưng chưa thể thay đổi avt của các đoạn chat cũ</t>
+  </si>
+  <si>
     <t>Sent_empty_message</t>
   </si>
   <si>
@@ -155,6 +227,9 @@
     <t>Nút gửi bị vô hiệu hóa hoặc hệ thống báo lỗi, không gửi tin nhắn rỗng lên Server.</t>
   </si>
   <si>
+    <t>12 : khi không có tin nhắn thì nhấn enter không gửi được gì</t>
+  </si>
+  <si>
     <t>Sent_max_length_text</t>
   </si>
   <si>
@@ -164,6 +239,9 @@
     <t>Hệ thống ngăn không cho nhập tiếp hoặc tự động cắt ngắn/báo lỗi quá ký tự.</t>
   </si>
   <si>
+    <t xml:space="preserve">13 : hệ thống không cho nhập tiếp khi đã đạt được n kí tự </t>
+  </si>
+  <si>
     <t>Sent_huge_image</t>
   </si>
   <si>
@@ -173,6 +251,9 @@
     <t>Hệ thống giới hạn dung lượng, hiển thị cảnh báo file quá kích thước cho phép.</t>
   </si>
   <si>
+    <t>14 : server chặn không cho gửi các file quá lớn ( đã test với file 1gb)</t>
+  </si>
+  <si>
     <t>Sent_invalid_image_format</t>
   </si>
   <si>
@@ -182,6 +263,9 @@
     <t>Server kiểm tra mã file, từ chối file lỗi và hiển thị thông báo "Định dạng không hợp lệ".</t>
   </si>
   <si>
+    <t xml:space="preserve">15 : không crash nhưng client vẫn dùng file đó để làm avt được và avt sẽ chuyển thành mặc định </t>
+  </si>
+  <si>
     <t>Client_disconnect_suddenly</t>
   </si>
   <si>
@@ -191,6 +275,9 @@
     <t>Server nhận biết client mất kết nối (sau khoảng timeout), chuyển trạng thái client thành offline. Client hiển thị "Đang kết nối lại...".</t>
   </si>
   <si>
+    <t>16 : mất kết nói sẽ trở về màn hình đăng nhập</t>
+  </si>
+  <si>
     <t>Client_reconnect</t>
   </si>
   <si>
@@ -200,6 +287,9 @@
     <t>Client tự động kết nối lại thành công với Server mà không cần khởi động lại app; nhận được các tin nhắn bị lỡ.</t>
   </si>
   <si>
+    <t>17 : client vẫn nhận được tin nhắn mới khi đăng nhập lại không bị lỡ</t>
+  </si>
+  <si>
     <t>Server_shutdown_unexpectedly</t>
   </si>
   <si>
@@ -209,6 +299,9 @@
     <t>Tất cả Client nhận được thông báo mất kết nối với Server, các chức năng gửi tin nhắn bị khóa tạm thời.</t>
   </si>
   <si>
+    <t>18 : các client sẽ mất kết nối và trở về màn hình đăng nhập</t>
+  </si>
+  <si>
     <t>Forward_to_multiple_clients</t>
   </si>
   <si>
@@ -218,6 +311,9 @@
     <t>Tin nhắn được gửi đồng thời đến tất cả các Client được chọn một cách chính xác.</t>
   </si>
   <si>
+    <t>19 : chưa có chức năng chuyển tiếp</t>
+  </si>
+  <si>
     <t>Reply_deleted_message</t>
   </si>
   <si>
@@ -227,6 +323,9 @@
     <t>Hệ thống xử lý mượt mà, hiển thị tin nhắn gốc dưới dạng "Tin nhắn đã bị xóa" trong phần Reply.</t>
   </si>
   <si>
+    <t>20 : hiển thị tin nhắn đã bị xóa và không thể rely tin nhắn đã bị xóa</t>
+  </si>
+  <si>
     <t>Concurrent_messages</t>
   </si>
   <si>
@@ -236,6 +335,9 @@
     <t>Server xử lý đồng bộ (Concurrency Management), tin nhắn của các client xếp hàng và hiển thị đúng thứ tự thời gian trên tất cả các client.</t>
   </si>
   <si>
+    <t>21 : đã đạt</t>
+  </si>
+  <si>
     <t>Duplicate_login</t>
   </si>
   <si>
@@ -245,6 +347,9 @@
     <t>Client đầu tiên bị đăng xuất tự động kèm thông báo "Tài khoản được đăng nhập từ thiết bị khác".</t>
   </si>
   <si>
+    <t>22 : 1 tài khoản có thể được đăng nhập trên 2 máy</t>
+  </si>
+  <si>
     <t>SQL_Injection_chat</t>
   </si>
   <si>
@@ -254,6 +359,9 @@
     <t>Server/Client mã hóa dữ liệu (Sanitize/Escape), hiển thị dưới dạng text thuần túy, không bị lỗi bảo mật hoặc thực thi script.</t>
   </si>
   <si>
+    <t>23 : đã mã hóa nên server không bị ảnh hưởng khi nhập ' OR '1'='1 vào ô user name</t>
+  </si>
+  <si>
     <t>Login_success</t>
   </si>
   <si>
@@ -263,6 +371,9 @@
     <t>Đăng nhập thành công, chuyển hướng vào màn hình chat chính, hiển thị đúng thông tin user.</t>
   </si>
   <si>
+    <t>24 : đã thành công</t>
+  </si>
+  <si>
     <t>Login_wrong_password</t>
   </si>
   <si>
@@ -272,6 +383,9 @@
     <t>Hiển thị thông báo lỗi rõ ràng: "Mật khẩu không chính xác", không cho phép vào hệ thống.</t>
   </si>
   <si>
+    <t xml:space="preserve">25 : không cho vào khi sai mật khẩu </t>
+  </si>
+  <si>
     <t>Login_non_existent_user</t>
   </si>
   <si>
@@ -281,6 +395,9 @@
     <t>Hiển thị thông báo lỗi thích hợp (ví dụ: "Tài khoản không tồn tại").</t>
   </si>
   <si>
+    <t>26 : hiển thị tài khoản và mật khẩu chưa chính xác</t>
+  </si>
+  <si>
     <t>Login_empty_fields</t>
   </si>
   <si>
@@ -290,6 +407,9 @@
     <t>Hệ thống báo lỗi ngay tại client (Validation) yêu cầu nhập đầy đủ, không gửi request rỗng lên Server.</t>
   </si>
   <si>
+    <t>27 : không thể đăng nhập</t>
+  </si>
+  <si>
     <t>Login_brute_force_protection</t>
   </si>
   <si>
@@ -299,6 +419,9 @@
     <t>Hệ thống tạm thời khóa tài khoản hoặc bắt nhập CAPTCHA / hiển thị đếm ngược thời gian chờ (ví dụ: "Thử lại sau 30 giây").</t>
   </si>
   <si>
+    <t>28 : chưa có cơ chế chống bruteforce</t>
+  </si>
+  <si>
     <t>Login_case_sensitivity</t>
   </si>
   <si>
@@ -308,6 +431,9 @@
     <t>Hệ thống từ chối đăng nhập (vì mật khẩu bắt buộc phải phân biệt chữ hoa/chữ thường).</t>
   </si>
   <si>
+    <t>29 : không thể đăng nhập</t>
+  </si>
+  <si>
     <t>Login_sql_injection</t>
   </si>
   <si>
@@ -317,6 +443,9 @@
     <t>Hệ thống báo lỗi tài khoản không hợp lệ, tuyệt đối không được để lọt qua cửa đăng nhập.</t>
   </si>
   <si>
+    <t xml:space="preserve">30 : không thể đăng nhập </t>
+  </si>
+  <si>
     <t>Login_trim_whitespace</t>
   </si>
   <si>
@@ -326,6 +455,9 @@
     <t>Hệ thống tự động cắt bỏ khoảng trắng thừa (Trim) và vẫn cho phép đăng nhập thành công (nếu ký tự gốc đúng).</t>
   </si>
   <si>
+    <t xml:space="preserve">31 : đăng nhập thành </t>
+  </si>
+  <si>
     <t>Login_session_timeout</t>
   </si>
   <si>
@@ -335,6 +467,9 @@
     <t>Khi người dùng tương tác lại (ví dụ: gửi tin nhắn), hệ thống tự động đẩy ra màn hình Login và yêu cầu đăng nhập lại.</t>
   </si>
   <si>
+    <t>32 : chưa có cơ chế session</t>
+  </si>
+  <si>
     <t>Login_network_interrupted</t>
   </si>
   <si>
@@ -342,6 +477,9 @@
   </si>
   <si>
     <t>Hệ thống hiển thị trạng thái loading (hoặc timeout) và báo lỗi "Kết nối mạng không ổn định", không bị crash app.</t>
+  </si>
+  <si>
+    <t>33 : không thể đăng nhập khi không kết nối được với server</t>
   </si>
 </sst>
 </file>
@@ -515,12 +653,30 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -686,12 +842,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -841,7 +991,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -865,16 +1015,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -883,94 +1033,109 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1247,6 +1412,1035 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>129540</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="5615940" cy="1043940"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="1844040" cy="2453640"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing11.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>15240</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="6438900" cy="1295400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>53340</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>137160</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2491740" cy="1600200"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2743200" cy="2567940"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing14.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>243840</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="8168640" cy="6332220"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing15.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>15240</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="8001000" cy="6598920"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing16.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>15240</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="8001000" cy="6598920"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing17.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>350520</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>83820</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="8275320" cy="6301740"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing18.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>205740</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>45720</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="8130540" cy="6263640"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing19.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>236220</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>106680</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="8161020" cy="6324600"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>243840</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="8168640" cy="6339840"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing20.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>243840</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>83820</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="8168640" cy="6301740"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing21.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>243840</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="8168640" cy="6339840"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>167640</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>83820</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7924800" y="0"/>
+          <a:ext cx="8092440" cy="6301740"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>541020</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1" r:link="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="6637020" cy="5273040"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>541020</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1" r:link="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="6637020" cy="5273040"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>320040</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="3977640" cy="952500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>53340</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>91440</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="1882140" cy="1188720"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>396240</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="5882640" cy="1615440"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>53340</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2552700" cy="2796540"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="3124200" cy="1943100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="WPS">
   <a:themeElements>
@@ -1502,10 +2696,10 @@
   <cols>
     <col min="1" max="1" width="8.30555555555556" customWidth="1"/>
     <col min="2" max="2" width="30.3333333333333" customWidth="1"/>
-    <col min="3" max="3" width="96.1296296296296" customWidth="1"/>
-    <col min="4" max="4" width="78.1574074074074" customWidth="1"/>
+    <col min="3" max="3" width="95.4444444444444" customWidth="1"/>
+    <col min="4" max="4" width="12.8888888888889" customWidth="1"/>
     <col min="5" max="5" width="114.009259259259" customWidth="1"/>
-    <col min="6" max="6" width="31.9722222222222" customWidth="1"/>
+    <col min="6" max="6" width="81" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1538,8 +2732,14 @@
       <c r="C2" t="s">
         <v>7</v>
       </c>
+      <c r="D2" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -1548,13 +2748,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>13</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -1563,13 +2769,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>16</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="E4" t="s">
-        <v>14</v>
+        <v>17</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -1578,13 +2790,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
+        <v>20</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="E5" t="s">
-        <v>17</v>
+        <v>21</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -1593,13 +2811,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
+        <v>24</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="E6" t="s">
-        <v>20</v>
+        <v>25</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1608,13 +2832,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>28</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="E7" t="s">
-        <v>23</v>
+        <v>29</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1623,13 +2853,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C8" t="s">
-        <v>25</v>
+        <v>32</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="E8" t="s">
-        <v>26</v>
+        <v>33</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1638,13 +2874,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="C9" t="s">
-        <v>28</v>
+        <v>36</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="E9" t="s">
-        <v>29</v>
+        <v>37</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1653,13 +2895,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="C10" t="s">
-        <v>31</v>
+        <v>40</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="E10" t="s">
-        <v>32</v>
+        <v>41</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1668,13 +2916,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="C11" t="s">
-        <v>34</v>
+        <v>44</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>45</v>
       </c>
       <c r="E11" t="s">
-        <v>35</v>
+        <v>46</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1683,13 +2937,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="C12" t="s">
-        <v>37</v>
+        <v>49</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="E12" t="s">
-        <v>38</v>
+        <v>50</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1698,13 +2958,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="C13" t="s">
-        <v>40</v>
+        <v>53</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="E13" t="s">
-        <v>41</v>
+        <v>54</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1713,13 +2979,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="C14" t="s">
-        <v>43</v>
+        <v>57</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="E14" t="s">
-        <v>44</v>
+        <v>58</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1728,13 +3000,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="C15" t="s">
-        <v>46</v>
+        <v>61</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="E15" t="s">
-        <v>47</v>
+        <v>62</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1743,287 +3021,785 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="C16" t="s">
-        <v>49</v>
+        <v>65</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>45</v>
       </c>
       <c r="E16" t="s">
-        <v>50</v>
+        <v>66</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>67</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:6">
       <c r="A17">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="C17" t="s">
-        <v>52</v>
+        <v>69</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="E17" t="s">
-        <v>53</v>
+        <v>70</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>71</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:6">
       <c r="A18">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="C18" t="s">
-        <v>55</v>
+        <v>73</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="E18" t="s">
-        <v>56</v>
+        <v>74</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>75</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:6">
       <c r="A19">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="C19" t="s">
-        <v>58</v>
+        <v>77</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="E19" t="s">
-        <v>59</v>
+        <v>78</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>79</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:6">
       <c r="A20">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="C20" t="s">
-        <v>61</v>
+        <v>81</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>45</v>
       </c>
       <c r="E20" t="s">
-        <v>62</v>
+        <v>82</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:6">
       <c r="A21">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="C21" t="s">
-        <v>64</v>
+        <v>85</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="E21" t="s">
-        <v>65</v>
+        <v>86</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>87</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:6">
       <c r="A22">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="C22" t="s">
-        <v>67</v>
+        <v>89</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="E22" t="s">
-        <v>68</v>
+        <v>90</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>91</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:6">
       <c r="A23">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="C23" t="s">
-        <v>70</v>
+        <v>93</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>45</v>
       </c>
       <c r="E23" t="s">
-        <v>71</v>
+        <v>94</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>95</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:6">
       <c r="A24">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="C24" t="s">
-        <v>73</v>
+        <v>97</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="E24" t="s">
-        <v>74</v>
+        <v>98</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>99</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:6">
       <c r="A25">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="C25" t="s">
-        <v>76</v>
+        <v>101</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="E25" t="s">
-        <v>77</v>
+        <v>102</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>103</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:6">
       <c r="A26">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>78</v>
+        <v>104</v>
       </c>
       <c r="C26" t="s">
-        <v>79</v>
+        <v>105</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="E26" t="s">
-        <v>80</v>
+        <v>106</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>107</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:6">
       <c r="A27">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>81</v>
+        <v>108</v>
       </c>
       <c r="C27" t="s">
-        <v>82</v>
+        <v>109</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="E27" t="s">
-        <v>83</v>
+        <v>110</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>111</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:6">
       <c r="A28">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>84</v>
+        <v>112</v>
       </c>
       <c r="C28" t="s">
-        <v>85</v>
+        <v>113</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="E28" t="s">
-        <v>86</v>
+        <v>114</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>115</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:6">
       <c r="A29">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>87</v>
+        <v>116</v>
       </c>
       <c r="C29" t="s">
-        <v>88</v>
+        <v>117</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>45</v>
       </c>
       <c r="E29" t="s">
-        <v>89</v>
+        <v>118</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>119</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:6">
       <c r="A30">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="C30" t="s">
-        <v>91</v>
+        <v>121</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="E30" t="s">
-        <v>92</v>
+        <v>122</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>123</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:6">
       <c r="A31">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="C31" t="s">
-        <v>94</v>
+        <v>125</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="E31" t="s">
-        <v>95</v>
+        <v>126</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>127</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:6">
       <c r="A32">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>96</v>
+        <v>128</v>
       </c>
       <c r="C32" t="s">
-        <v>97</v>
+        <v>129</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="E32" t="s">
-        <v>98</v>
+        <v>130</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>131</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:6">
       <c r="A33">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>99</v>
+        <v>132</v>
       </c>
       <c r="C33" t="s">
-        <v>100</v>
+        <v>133</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>45</v>
       </c>
       <c r="E33" t="s">
-        <v>101</v>
+        <v>134</v>
+      </c>
+      <c r="F33" s="5" t="s">
+        <v>135</v>
       </c>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:6">
       <c r="A34">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>102</v>
+        <v>136</v>
       </c>
       <c r="C34" t="s">
-        <v>103</v>
+        <v>137</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="E34" t="s">
-        <v>104</v>
+        <v>138</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>139</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/Extra/TestCase001.xlsx
+++ b/Extra/TestCase001.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="8400"/>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="test_case" sheetId="1" r:id="rId1"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="136">
   <si>
     <t>TestCase</t>
   </si>
@@ -458,18 +458,6 @@
     <t xml:space="preserve">31 : đăng nhập thành </t>
   </si>
   <si>
-    <t>Login_session_timeout</t>
-  </si>
-  <si>
-    <t>Đăng nhập thành công, sau đó treo ứng dụng/để máy treo qua đêm (hết hạn Session/Token).</t>
-  </si>
-  <si>
-    <t>Khi người dùng tương tác lại (ví dụ: gửi tin nhắn), hệ thống tự động đẩy ra màn hình Login và yêu cầu đăng nhập lại.</t>
-  </si>
-  <si>
-    <t>32 : chưa có cơ chế session</t>
-  </si>
-  <si>
     <t>Login_network_interrupted</t>
   </si>
   <si>
@@ -479,7 +467,7 @@
     <t>Hệ thống hiển thị trạng thái loading (hoặc timeout) và báo lỗi "Kết nối mạng không ổn định", không bị crash app.</t>
   </si>
   <si>
-    <t>33 : không thể đăng nhập khi không kết nối được với server</t>
+    <t>32 : không thể đăng nhập khi không kết nối được với server</t>
   </si>
 </sst>
 </file>
@@ -668,13 +656,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1102,7 +1090,7 @@
     <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1115,7 +1103,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1125,6 +1113,12 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
@@ -1132,9 +1126,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2948,7 +2939,7 @@
       <c r="E12" t="s">
         <v>50</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="F12" s="3" t="s">
         <v>51</v>
       </c>
     </row>
@@ -3011,7 +3002,7 @@
       <c r="E15" t="s">
         <v>62</v>
       </c>
-      <c r="F15" s="6" t="s">
+      <c r="F15" s="3" t="s">
         <v>63</v>
       </c>
     </row>
@@ -3053,7 +3044,7 @@
       <c r="E17" t="s">
         <v>70</v>
       </c>
-      <c r="F17" s="6" t="s">
+      <c r="F17" s="3" t="s">
         <v>71</v>
       </c>
     </row>
@@ -3074,7 +3065,7 @@
       <c r="E18" t="s">
         <v>74</v>
       </c>
-      <c r="F18" s="6" t="s">
+      <c r="F18" s="3" t="s">
         <v>75</v>
       </c>
     </row>
@@ -3095,7 +3086,7 @@
       <c r="E19" t="s">
         <v>78</v>
       </c>
-      <c r="F19" s="6" t="s">
+      <c r="F19" s="3" t="s">
         <v>79</v>
       </c>
     </row>
@@ -3137,7 +3128,7 @@
       <c r="E21" t="s">
         <v>86</v>
       </c>
-      <c r="F21" s="6" t="s">
+      <c r="F21" s="3" t="s">
         <v>87</v>
       </c>
     </row>
@@ -3158,7 +3149,7 @@
       <c r="E22" t="s">
         <v>90</v>
       </c>
-      <c r="F22" s="6" t="s">
+      <c r="F22" s="3" t="s">
         <v>91</v>
       </c>
     </row>
@@ -3200,7 +3191,7 @@
       <c r="E24" t="s">
         <v>98</v>
       </c>
-      <c r="F24" s="6" t="s">
+      <c r="F24" s="3" t="s">
         <v>99</v>
       </c>
     </row>
@@ -3221,7 +3212,7 @@
       <c r="E25" t="s">
         <v>102</v>
       </c>
-      <c r="F25" s="6" t="s">
+      <c r="F25" s="3" t="s">
         <v>103</v>
       </c>
     </row>
@@ -3242,7 +3233,7 @@
       <c r="E26" t="s">
         <v>106</v>
       </c>
-      <c r="F26" s="6" t="s">
+      <c r="F26" s="3" t="s">
         <v>107</v>
       </c>
     </row>
@@ -3263,7 +3254,7 @@
       <c r="E27" t="s">
         <v>110</v>
       </c>
-      <c r="F27" s="6" t="s">
+      <c r="F27" s="3" t="s">
         <v>111</v>
       </c>
     </row>
@@ -3284,7 +3275,7 @@
       <c r="E28" t="s">
         <v>114</v>
       </c>
-      <c r="F28" s="6" t="s">
+      <c r="F28" s="3" t="s">
         <v>115</v>
       </c>
     </row>
@@ -3326,7 +3317,7 @@
       <c r="E30" t="s">
         <v>122</v>
       </c>
-      <c r="F30" s="6" t="s">
+      <c r="F30" s="3" t="s">
         <v>123</v>
       </c>
     </row>
@@ -3347,7 +3338,7 @@
       <c r="E31" t="s">
         <v>126</v>
       </c>
-      <c r="F31" s="6" t="s">
+      <c r="F31" s="3" t="s">
         <v>127</v>
       </c>
     </row>
@@ -3368,7 +3359,7 @@
       <c r="E32" t="s">
         <v>130</v>
       </c>
-      <c r="F32" s="6" t="s">
+      <c r="F32" s="3" t="s">
         <v>131</v>
       </c>
     </row>
@@ -3383,36 +3374,20 @@
       <c r="C33" t="s">
         <v>133</v>
       </c>
-      <c r="D33" s="4" t="s">
-        <v>45</v>
+      <c r="D33" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="E33" t="s">
         <v>134</v>
       </c>
-      <c r="F33" s="5" t="s">
+      <c r="F33" s="3" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="34" spans="1:6">
-      <c r="A34">
-        <f t="shared" si="0"/>
-        <v>33</v>
-      </c>
-      <c r="B34" t="s">
-        <v>136</v>
-      </c>
-      <c r="C34" t="s">
-        <v>137</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E34" t="s">
-        <v>138</v>
-      </c>
-      <c r="F34" s="6" t="s">
-        <v>139</v>
-      </c>
+      <c r="D34" s="6"/>
+      <c r="E34"/>
+      <c r="F34" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
